--- a/Penman_irrigation_results.xlsx
+++ b/Penman_irrigation_results.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC53"/>
+  <dimension ref="A1:BC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9378,6 +9378,105 @@
         <v>19.4368</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Penman_irrigation_results.xlsx
+++ b/Penman_irrigation_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penman_irrigation_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Penman_irrigation_results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC54"/>
+  <dimension ref="A1:BC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,25 +9216,25 @@
         <v>45474</v>
       </c>
       <c r="B53" t="n">
-        <v>2.3056</v>
+        <v>2.1924</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>445.1</v>
+        <v>372.4167</v>
       </c>
       <c r="E53" t="n">
-        <v>16.95</v>
+        <v>16.9676</v>
       </c>
       <c r="F53" t="n">
-        <v>68</v>
+        <v>68.66670000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>1.9316</v>
+        <v>1.9338</v>
       </c>
       <c r="H53" t="n">
-        <v>13.1349</v>
+        <v>13.2784</v>
       </c>
       <c r="I53" t="n">
         <v>-0.0005</v>
@@ -9249,16 +9249,16 @@
         <v>0.0645</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6181</v>
+        <v>0.606</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1225</v>
+        <v>0.1226</v>
       </c>
       <c r="O53" t="n">
-        <v>18.7895</v>
+        <v>16.1171</v>
       </c>
       <c r="P53" t="n">
-        <v>0.2029</v>
+        <v>0.1795</v>
       </c>
       <c r="Q53" t="n">
         <v>27</v>
@@ -9276,10 +9276,10 @@
         <v>0.875</v>
       </c>
       <c r="V53" t="n">
-        <v>0.1944</v>
+        <v>0.172</v>
       </c>
       <c r="W53" t="n">
-        <v>0.1775</v>
+        <v>0.157</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -9324,22 +9324,22 @@
         <v>5.1248</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.1944</v>
+        <v>0.172</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5486</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.5604</v>
+        <v>0.538</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.1803</v>
+        <v>0.1598</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.1944</v>
+        <v>0.172</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.0146</v>
+        <v>0.9941</v>
       </c>
       <c r="AR53" t="n">
         <v>0</v>
@@ -9360,50 +9360,94 @@
         <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>3.7245</v>
+        <v>3.2946</v>
       </c>
       <c r="AY53" t="n">
-        <v>10.9017</v>
+        <v>10.5091</v>
       </c>
       <c r="AZ53" t="n">
-        <v>10.7358</v>
+        <v>10.3058</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.4534</v>
+        <v>3.0608</v>
       </c>
       <c r="BB53" t="n">
-        <v>3.7245</v>
+        <v>3.2946</v>
       </c>
       <c r="BC53" t="n">
-        <v>19.4368</v>
+        <v>19.0442</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
         <v>45475</v>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>2.4895</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>343.9583</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22.6829</v>
+      </c>
+      <c r="F54" t="n">
+        <v>57.3542</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.756</v>
+      </c>
+      <c r="H54" t="n">
+        <v>15.8068</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="J54" t="n">
+        <v>183</v>
+      </c>
+      <c r="K54" t="n">
+        <v>97.566</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="O54" t="n">
+        <v>15.1107</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>27</v>
+      </c>
+      <c r="R54" t="n">
+        <v>9</v>
+      </c>
+      <c r="S54" t="n">
+        <v>7</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.9583</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.1931</v>
+      </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
@@ -9423,13 +9467,13 @@
         <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.0912</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.0912</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -9446,12 +9490,24 @@
       <c r="AK54" t="n">
         <v>5.22</v>
       </c>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
+      <c r="AL54" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.1872</v>
+      </c>
       <c r="AR54" t="n">
         <v>0</v>
       </c>
@@ -9470,12 +9526,191 @@
       <c r="AW54" t="n">
         <v>0</v>
       </c>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-      <c r="BB54" t="inlineStr"/>
-      <c r="BC54" t="inlineStr"/>
+      <c r="AX54" t="n">
+        <v>5.5985</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>14.2079</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>12.6098</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>6.7596</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>7.3456</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>22.743</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.0101</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7.1333</v>
+      </c>
+      <c r="E55" t="n">
+        <v>22.9778</v>
+      </c>
+      <c r="F55" t="n">
+        <v>67.5333</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.8057</v>
+      </c>
+      <c r="H55" t="n">
+        <v>18.9476</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="J55" t="n">
+        <v>184</v>
+      </c>
+      <c r="K55" t="n">
+        <v>97.569</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.2287</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>27</v>
+      </c>
+      <c r="R55" t="n">
+        <v>9</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.9583</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0.8213</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.7454</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.1804</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>15.7329</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>8.284599999999999</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>9.0159</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>22.6128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
